--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2468,6 +2468,73 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>12:47:19</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424000CE</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>159.15</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>672.75</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>nifty_tp</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>279</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>100672.75</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2535,6 +2535,274 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>12:54:50</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424050CE</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>8186.75</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>nifty_tp</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>205</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>108186.75</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>13:00:22</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424050CE</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>136.05</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>-2574</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>nifty_sl</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>105612.75</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>13:05:31</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424050CE</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>139.15</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>6045</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>nifty_tp</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>111657.75</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>13:09:51</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424050CE</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>138.55</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>5957.25</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>nifty_tp</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>178</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>117615</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1120,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1641,7 +1640,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1961,7 +1959,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2144,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -2400,7 +2396,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -2802,6 +2797,143 @@
           <t>no</t>
         </is>
       </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>13:25:16</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424050CE</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>98570</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>13:25:16</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>─ SUMMARY ─</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr"/>
+      <c r="E42" s="11" t="inlineStr"/>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="12" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Daily loss limit ₹300.0 hit</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="12" t="n">
+        <v>98570</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O42" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,6 +1120,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1640,6 +1641,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1959,6 +1961,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -2144,6 +2147,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
@@ -2396,6 +2400,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -2916,24 +2921,259 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>10:16:01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>120.85</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>-975</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>518</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>99025</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>10:16:01</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>─ SUMMARY ─</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr"/>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="12" t="n">
+        <v>-975</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>Daily loss limit ₹300.0 hit</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="12" t="n">
+        <v>99025</v>
+      </c>
+      <c r="N45" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P45" s="12" t="n">
+        <v>-975</v>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>10:23:11</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200PE</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>100117</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>10:32:50</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>-94.25</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>nifty_sl</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>100022.75</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3175,6 +3175,594 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>11:22:51</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200PE</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>nifty_reversal</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>11:49:27</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>-48.75</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>trail</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>99951.25</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>12:00:26</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>nifty_reversal</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>100146.25</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>12:01:10</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>-91</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>trail</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>100055.25</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>14:58:27</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200CE</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>-380.25</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>nifty_sl</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>99619.75</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>14:58:27</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>─ SUMMARY ─</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="12" t="n">
+        <v>-380.25</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>Daily loss limit ₹300.0 hit</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="12" t="n">
+        <v>99619.75</v>
+      </c>
+      <c r="N54" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O54" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P54" s="12" t="n">
+        <v>-380.25</v>
+      </c>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>15:07:55</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200PE</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>nifty_sl</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>99990.25</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>15:10:55</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200PE</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>-78</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>nifty_sl</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>99912.25</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>15:16:54</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>NIFTY2671424200PE</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>287</v>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>100737.75</v>
+      </c>
+      <c r="N58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
